--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -476,7 +476,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -638,6 +638,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -647,7 +650,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -808,6 +811,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -851,7 +857,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1013,6 +1019,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1022,7 +1031,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1184,6 +1193,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>15523855.279351614</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15858152.82628401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1226,7 +1238,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1388,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1397,7 +1412,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1559,6 +1574,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5085531.097460622</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5419828.6443930175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1580,11 +1598,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="342668416"/>
-        <c:axId val="342670336"/>
+        <c:axId val="107766144"/>
+        <c:axId val="107768448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="342668416"/>
+        <c:axId val="107766144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1627,14 +1645,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342670336"/>
+        <c:crossAx val="107768448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="342670336"/>
+        <c:axId val="107768448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1685,7 +1703,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342668416"/>
+        <c:crossAx val="107766144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1876,7 +1894,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2038,6 +2056,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-127166.75771952557</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-218860.88907832516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2052,8 +2073,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="342748544"/>
-        <c:axId val="342747008"/>
+        <c:axId val="160257536"/>
+        <c:axId val="160255360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2078,7 +2099,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2240,6 +2261,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2249,7 +2273,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2411,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2427,11 +2454,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="342692224"/>
-        <c:axId val="342694144"/>
+        <c:axId val="160251904"/>
+        <c:axId val="160253824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="342692224"/>
+        <c:axId val="160251904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2474,14 +2501,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342694144"/>
+        <c:crossAx val="160253824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="342694144"/>
+        <c:axId val="160253824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2532,12 +2559,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342692224"/>
+        <c:crossAx val="160251904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="342747008"/>
+        <c:axId val="160255360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2574,12 +2601,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342748544"/>
+        <c:crossAx val="160257536"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="342748544"/>
+        <c:axId val="160257536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2588,7 +2615,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="342747008"/>
+        <c:crossAx val="160255360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2997,7 +3024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5555,6 +5582,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:13" ht="12.75">
+      <c r="A57" s="11">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="12">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="12">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="13">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="13">
+        <v>-218860.88907832516</v>
+      </c>
+      <c r="F57" s="14">
+        <v>-205696.32229368878</v>
+      </c>
+      <c r="G57" s="14">
+        <v>13723339.905224066</v>
+      </c>
+      <c r="H57" s="14">
+        <v>14601633.803121971</v>
+      </c>
+      <c r="I57" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J57" s="14">
+        <v>15858152.82628401</v>
+      </c>
+      <c r="K57" s="14">
+        <v>5419828.6443930175</v>
+      </c>
+      <c r="L57" s="13">
+        <v>1256519.0231620383</v>
+      </c>
+      <c r="M57" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -476,7 +476,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -641,6 +641,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -650,7 +653,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -814,6 +817,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -857,7 +863,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1022,6 +1028,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,7 +1040,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1196,6 +1205,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15858152.82628401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15967939.768014949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1238,7 +1250,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1403,6 +1415,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1412,7 +1427,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1577,6 +1592,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5419828.6443930175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5529615.5861239564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1598,11 +1616,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="107766144"/>
-        <c:axId val="107768448"/>
+        <c:axId val="96813056"/>
+        <c:axId val="96814976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="107766144"/>
+        <c:axId val="96813056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1645,14 +1663,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="107768448"/>
+        <c:crossAx val="96814976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="107768448"/>
+        <c:axId val="96814976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1703,7 +1721,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="107766144"/>
+        <c:crossAx val="96813056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1894,7 +1912,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2059,6 +2077,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-218860.88907832516</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-259981.61012664012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2073,8 +2094,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="160257536"/>
-        <c:axId val="160255360"/>
+        <c:axId val="97829632"/>
+        <c:axId val="97827456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2099,7 +2120,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2264,6 +2285,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,7 +2297,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2438,6 +2462,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2454,11 +2481,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="160251904"/>
-        <c:axId val="160253824"/>
+        <c:axId val="96856704"/>
+        <c:axId val="97825536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="160251904"/>
+        <c:axId val="96856704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2501,14 +2528,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160253824"/>
+        <c:crossAx val="97825536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160253824"/>
+        <c:axId val="97825536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,12 +2586,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160251904"/>
+        <c:crossAx val="96856704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="160255360"/>
+        <c:axId val="97827456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2601,12 +2628,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160257536"/>
+        <c:crossAx val="97829632"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="160257536"/>
+        <c:axId val="97829632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2615,7 +2642,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="160255360"/>
+        <c:crossAx val="97827456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3024,7 +3051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5623,6 +5650,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:13" ht="12.75">
+      <c r="A58" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="12">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="12">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="13">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="13">
+        <v>-259981.61012664012</v>
+      </c>
+      <c r="F58" s="14">
+        <v>-242520.15265919158</v>
+      </c>
+      <c r="G58" s="14">
+        <v>13480819.752564875</v>
+      </c>
+      <c r="H58" s="14">
+        <v>14451439.134726271</v>
+      </c>
+      <c r="I58" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J58" s="14">
+        <v>15967939.768014949</v>
+      </c>
+      <c r="K58" s="14">
+        <v>5529615.5861239564</v>
+      </c>
+      <c r="L58" s="13">
+        <v>1516500.6332886785</v>
+      </c>
+      <c r="M58" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,6 +75,10 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -476,7 +480,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -644,6 +648,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -653,7 +660,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -820,6 +827,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -863,7 +873,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1031,6 +1041,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,7 +1053,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1208,6 +1221,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15967939.768014949</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16008382.510111498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1250,7 +1266,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1418,6 +1434,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1427,7 +1446,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1595,6 +1614,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5529615.5861239564</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5570058.3282205053</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1616,11 +1638,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="96813056"/>
-        <c:axId val="96814976"/>
+        <c:axId val="389091712"/>
+        <c:axId val="389094400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="96813056"/>
+        <c:axId val="389091712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1663,14 +1685,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96814976"/>
+        <c:crossAx val="389094400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="96814976"/>
+        <c:axId val="389094400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1721,7 +1743,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96813056"/>
+        <c:crossAx val="389091712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1912,7 +1934,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2080,6 +2102,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-259981.61012664012</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-239860.56658340184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2094,8 +2119,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="97829632"/>
-        <c:axId val="97827456"/>
+        <c:axId val="389133824"/>
+        <c:axId val="389123456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2120,7 +2145,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2288,6 +2313,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2297,7 +2325,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2465,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,11 +2512,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="96856704"/>
-        <c:axId val="97825536"/>
+        <c:axId val="389120000"/>
+        <c:axId val="389121536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="96856704"/>
+        <c:axId val="389120000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2528,14 +2559,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97825536"/>
+        <c:crossAx val="389121536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="97825536"/>
+        <c:axId val="389121536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,12 +2617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96856704"/>
+        <c:crossAx val="389120000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="97827456"/>
+        <c:axId val="389123456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2628,12 +2659,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97829632"/>
+        <c:crossAx val="389133824"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="97829632"/>
+        <c:axId val="389133824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2642,7 +2673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="97827456"/>
+        <c:crossAx val="389123456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3051,7 +3082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3185,28 +3216,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5688,6 +5719,47 @@
         <v>1516500.6332886785</v>
       </c>
       <c r="M58" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="12.75">
+      <c r="A59" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="12">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="12">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="13">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="13">
+        <v>-239860.56658340184</v>
+      </c>
+      <c r="F59" s="14">
+        <v>-223126.09855248407</v>
+      </c>
+      <c r="G59" s="14">
+        <v>13257693.654012391</v>
+      </c>
+      <c r="H59" s="14">
+        <v>14252021.310239417</v>
+      </c>
+      <c r="I59" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J59" s="14">
+        <v>16008382.510111498</v>
+      </c>
+      <c r="K59" s="14">
+        <v>5570058.3282205053</v>
+      </c>
+      <c r="L59" s="13">
+        <v>1756361.1998720802</v>
+      </c>
+      <c r="M59" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,10 +75,6 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -480,7 +476,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -651,6 +647,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,7 +659,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -830,6 +829,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -873,7 +875,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1044,6 +1046,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1053,7 +1058,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1224,6 +1229,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>16008382.510111498</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15650423.858476061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1266,7 +1274,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1437,6 +1445,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1446,7 +1457,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1617,6 +1628,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5570058.3282205053</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5212099.6765850689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1638,11 +1652,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="389091712"/>
-        <c:axId val="389094400"/>
+        <c:axId val="80231040"/>
+        <c:axId val="80237312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="389091712"/>
+        <c:axId val="80231040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1685,14 +1699,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389094400"/>
+        <c:crossAx val="80237312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="389094400"/>
+        <c:axId val="80237312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1743,7 +1757,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389091712"/>
+        <c:crossAx val="80231040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1934,7 +1948,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2105,6 +2119,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-239860.56658340184</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-153850.30177591741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2119,8 +2136,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="389133824"/>
-        <c:axId val="389123456"/>
+        <c:axId val="92017024"/>
+        <c:axId val="92014848"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2145,7 +2162,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2316,6 +2333,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2325,7 +2345,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2496,6 +2516,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2512,11 +2535,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="389120000"/>
-        <c:axId val="389121536"/>
+        <c:axId val="80262656"/>
+        <c:axId val="80264192"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="389120000"/>
+        <c:axId val="80262656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,14 +2582,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389121536"/>
+        <c:crossAx val="80264192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="389121536"/>
+        <c:axId val="80264192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2617,12 +2640,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389120000"/>
+        <c:crossAx val="80262656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="389123456"/>
+        <c:axId val="92014848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,12 +2682,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389133824"/>
+        <c:crossAx val="92017024"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="389133824"/>
+        <c:axId val="92017024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,7 +2696,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="389123456"/>
+        <c:crossAx val="92014848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3082,7 +3105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3216,28 +3239,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5760,6 +5783,47 @@
         <v>1756361.1998720802</v>
       </c>
       <c r="M59" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="12.75">
+      <c r="A60" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="12">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="12">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="13">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="13">
+        <v>-153850.30177591741</v>
+      </c>
+      <c r="F60" s="14">
+        <v>-146803.72614120715</v>
+      </c>
+      <c r="G60" s="14">
+        <v>13110889.927871184</v>
+      </c>
+      <c r="H60" s="14">
+        <v>13740212.356828064</v>
+      </c>
+      <c r="I60" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J60" s="14">
+        <v>15650423.858476061</v>
+      </c>
+      <c r="K60" s="14">
+        <v>5212099.6765850689</v>
+      </c>
+      <c r="L60" s="13">
+        <v>1910211.5016479976</v>
+      </c>
+      <c r="M60" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,6 +75,10 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -476,7 +480,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -650,6 +654,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -659,7 +666,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -832,6 +839,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -875,7 +885,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1049,6 +1059,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,7 +1071,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1232,6 +1245,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>15650423.858476061</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17341729.54692129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,7 +1290,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1448,6 +1464,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,7 +1476,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1631,6 +1650,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5212099.6765850689</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6903405.365030298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1652,11 +1674,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80231040"/>
-        <c:axId val="80237312"/>
+        <c:axId val="444281984"/>
+        <c:axId val="444298752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80231040"/>
+        <c:axId val="444281984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1699,14 +1721,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80237312"/>
+        <c:crossAx val="444298752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80237312"/>
+        <c:axId val="444298752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1757,7 +1779,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80231040"/>
+        <c:crossAx val="444281984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1948,7 +1970,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2122,6 +2144,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-153850.30177591741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-543896.52099822264</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2136,8 +2161,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="92017024"/>
-        <c:axId val="92014848"/>
+        <c:axId val="444336768"/>
+        <c:axId val="444334464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2162,7 +2187,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2336,6 +2361,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2345,7 +2373,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2519,6 +2547,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2535,11 +2566,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80262656"/>
-        <c:axId val="80264192"/>
+        <c:axId val="444330752"/>
+        <c:axId val="444332288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80262656"/>
+        <c:axId val="444330752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2582,14 +2613,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80264192"/>
+        <c:crossAx val="444332288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80264192"/>
+        <c:axId val="444332288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,12 +2671,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80262656"/>
+        <c:crossAx val="444330752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="92014848"/>
+        <c:axId val="444334464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2682,12 +2713,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92017024"/>
+        <c:crossAx val="444336768"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="92017024"/>
+        <c:axId val="444336768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2696,7 +2727,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="92014848"/>
+        <c:crossAx val="444334464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3105,7 +3136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3239,28 +3270,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5824,6 +5855,47 @@
         <v>1910211.5016479976</v>
       </c>
       <c r="M60" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="12.75">
+      <c r="A61" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="12">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="12">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="13">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="13">
+        <v>-543896.52099822264</v>
+      </c>
+      <c r="F61" s="14">
+        <v>-462104.07803294534</v>
+      </c>
+      <c r="G61" s="14">
+        <v>12648785.849838238</v>
+      </c>
+      <c r="H61" s="14">
+        <v>14887621.524275072</v>
+      </c>
+      <c r="I61" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J61" s="14">
+        <v>17341729.54692129</v>
+      </c>
+      <c r="K61" s="14">
+        <v>6903405.365030298</v>
+      </c>
+      <c r="L61" s="13">
+        <v>2454108.0226462204</v>
+      </c>
+      <c r="M61" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR)cn.xlsx
@@ -480,7 +480,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -657,6 +657,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -666,7 +669,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -842,6 +845,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -885,7 +891,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1062,6 +1068,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1071,7 +1080,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1248,6 +1257,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>17341729.54692129</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>18201846.466008939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1290,7 +1302,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1467,6 +1479,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1476,7 +1491,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1653,6 +1668,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6903405.365030298</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7763522.2841179464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1674,11 +1692,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444281984"/>
-        <c:axId val="444298752"/>
+        <c:axId val="438575104"/>
+        <c:axId val="438578560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444281984"/>
+        <c:axId val="438575104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1721,14 +1739,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444298752"/>
+        <c:crossAx val="438578560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444298752"/>
+        <c:axId val="438578560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1779,7 +1797,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444281984"/>
+        <c:crossAx val="438575104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1970,7 +1988,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2147,6 +2165,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-543896.52099822264</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-658295.54002827872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2161,8 +2182,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="444336768"/>
-        <c:axId val="444334464"/>
+        <c:axId val="440935552"/>
+        <c:axId val="438615424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2187,7 +2208,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2364,6 +2385,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2373,7 +2397,7 @@
               <c:f>'模型四 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2550,6 +2574,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2566,11 +2593,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444330752"/>
-        <c:axId val="444332288"/>
+        <c:axId val="438611968"/>
+        <c:axId val="438613888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444330752"/>
+        <c:axId val="438611968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2613,14 +2640,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444332288"/>
+        <c:crossAx val="438613888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444332288"/>
+        <c:axId val="438613888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2671,12 +2698,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444330752"/>
+        <c:crossAx val="438611968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="444334464"/>
+        <c:axId val="438615424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2713,12 +2740,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444336768"/>
+        <c:crossAx val="440935552"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="444336768"/>
+        <c:axId val="440935552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2727,7 +2754,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="444334464"/>
+        <c:crossAx val="438615424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3136,7 +3163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5899,6 +5926,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:13" ht="12.75">
+      <c r="A62" s="11">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="12">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="12">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="13">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="13">
+        <v>-658295.54002827872</v>
+      </c>
+      <c r="F62" s="14">
+        <v>-528751.43574859062</v>
+      </c>
+      <c r="G62" s="14">
+        <v>12120034.414089648</v>
+      </c>
+      <c r="H62" s="14">
+        <v>15089442.903334439</v>
+      </c>
+      <c r="I62" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J62" s="14">
+        <v>18201846.466008939</v>
+      </c>
+      <c r="K62" s="14">
+        <v>7763522.2841179464</v>
+      </c>
+      <c r="L62" s="13">
+        <v>3112403.5626744991</v>
+      </c>
+      <c r="M62" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">
